--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125908069</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125908045</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillkrogvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>529462</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6951250</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12525-2025 artfynd.xlsx
+++ b/artfynd/A 12525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908069</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>